--- a/acpython/検討資料.xlsx
+++ b/acpython/検討資料.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\github\nasu\PythonLibrary\acpython\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E6ECCE-A712-485F-941F-D390B64F2330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C822F09-22FB-414B-B689-5D5C4F868924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E4F5F74F-CE3A-4B04-BDB8-F19696AB784F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E4F5F74F-CE3A-4B04-BDB8-F19696AB784F}"/>
   </bookViews>
   <sheets>
     <sheet name="セグ木" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="153">
   <si>
     <t>Point</t>
     <phoneticPr fontId="1"/>
@@ -1079,6 +1079,18 @@
   </si>
   <si>
     <t>私用メモ: 畳み込めるものまとめ - noshi91のメモ</t>
+  </si>
+  <si>
+    <t>OK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FWT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FZT</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1172,7 +1184,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>566786</xdr:colOff>
+      <xdr:colOff>555356</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2233,8 +2245,14 @@
       <c r="B7" t="s">
         <v>118</v>
       </c>
+      <c r="C7" t="s">
+        <v>151</v>
+      </c>
       <c r="D7" t="s">
         <v>141</v>
+      </c>
+      <c r="F7" t="s">
+        <v>150</v>
       </c>
       <c r="K7" t="s">
         <v>140</v>
@@ -2247,8 +2265,14 @@
       <c r="B8" t="s">
         <v>119</v>
       </c>
+      <c r="C8" t="s">
+        <v>151</v>
+      </c>
       <c r="D8" t="s">
         <v>145</v>
+      </c>
+      <c r="F8" t="s">
+        <v>150</v>
       </c>
       <c r="K8" t="s">
         <v>141</v>
@@ -2261,6 +2285,9 @@
       <c r="B9" t="s">
         <v>120</v>
       </c>
+      <c r="C9" t="s">
+        <v>152</v>
+      </c>
       <c r="D9" t="s">
         <v>146</v>
       </c>
@@ -2275,6 +2302,9 @@
       <c r="B10" t="s">
         <v>121</v>
       </c>
+      <c r="C10" t="s">
+        <v>152</v>
+      </c>
       <c r="D10" t="s">
         <v>147</v>
       </c>
@@ -2326,6 +2356,9 @@
       </c>
       <c r="C15" t="s">
         <v>148</v>
+      </c>
+      <c r="F15" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">

--- a/acpython/検討資料.xlsx
+++ b/acpython/検討資料.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\github\nasu\PythonLibrary\acpython\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C822F09-22FB-414B-B689-5D5C4F868924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2AD077-66D0-4A7F-B922-BFEEFAA5EEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E4F5F74F-CE3A-4B04-BDB8-F19696AB784F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{E4F5F74F-CE3A-4B04-BDB8-F19696AB784F}"/>
   </bookViews>
   <sheets>
     <sheet name="セグ木" sheetId="1" r:id="rId1"/>
     <sheet name="木構造" sheetId="2" r:id="rId2"/>
     <sheet name="たたみ込み" sheetId="3" r:id="rId3"/>
+    <sheet name="場合の数" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="195">
   <si>
     <t>Point</t>
     <phoneticPr fontId="1"/>
@@ -1090,6 +1091,305 @@
   </si>
   <si>
     <t>FZT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>写像12相</t>
+    <rPh sb="0" eb="2">
+      <t>シャゾウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>玉</t>
+    <rPh sb="0" eb="1">
+      <t>タマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>区別する</t>
+  </si>
+  <si>
+    <t>区別する</t>
+    <rPh sb="0" eb="2">
+      <t>クベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>区別しない</t>
+    <rPh sb="0" eb="2">
+      <t>クベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>玉の個数</t>
+    <rPh sb="0" eb="1">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1個以内</t>
+    <rPh sb="1" eb="2">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1個以上</t>
+    <rPh sb="1" eb="2">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>条件なし</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>累乗①</t>
+    <rPh sb="0" eb="2">
+      <t>ルイジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分割数①</t>
+    <rPh sb="0" eb="2">
+      <t>ブンカツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分割数②</t>
+    <rPh sb="0" eb="2">
+      <t>ブンカツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>順列①</t>
+    <rPh sb="0" eb="2">
+      <t>ジュンレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>組合①</t>
+    <rPh sb="0" eb="1">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>組合②</t>
+    <rPh sb="0" eb="1">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>組合③</t>
+    <rPh sb="0" eb="1">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>組合④</t>
+    <rPh sb="0" eb="1">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スターリング①</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベル①</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>n個の玉をk個の箱に入れる数</t>
+    <rPh sb="1" eb="2">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>k^n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>O(log(n))</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>O(1) ※前計算O(k)</t>
+    <rPh sb="6" eb="9">
+      <t>マエケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kPn</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>組合</t>
+    <rPh sb="0" eb="1">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>順列</t>
+    <rPh sb="0" eb="2">
+      <t>ジュンレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>累乗</t>
+    <rPh sb="0" eb="2">
+      <t>ルイジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kCn</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(n+k-1)Cn</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>O(1) ※前計算O(n + k)</t>
+    <rPh sb="6" eb="9">
+      <t>マエケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(n-1)C(k-1)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>O(klog(n)) ※前計算O(n + k)</t>
+    <rPh sb="12" eb="15">
+      <t>マエケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sum(1_k)(-1)^(k-1)(kCi)i^n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スターリング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S(n, k)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>O(k^2log(n)) ※前計算O(n + k)</t>
+    <rPh sb="14" eb="17">
+      <t>マエケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B(n, k)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分割数</t>
+    <rPh sb="0" eb="2">
+      <t>ブンカツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分割数①</t>
+    <rPh sb="0" eb="3">
+      <t>ブンカツスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>O(nk)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1123,20 +1423,78 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1148,11 +1506,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2378,4 +2751,251 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F97022F-45A4-4C40-87D0-D3DF4DDFE11E}">
+  <dimension ref="B3:F34"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="14.296875" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.09765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="D4" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B5" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B7" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B8" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B9" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>166</v>
+      </c>
+      <c r="C17" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>167</v>
+      </c>
+      <c r="C20" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>169</v>
+      </c>
+      <c r="C22" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="C23" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>170</v>
+      </c>
+      <c r="C24" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>187</v>
+      </c>
+      <c r="C26" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C32" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
+        <v>165</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/acpython/検討資料.xlsx
+++ b/acpython/検討資料.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\github\nasu\PythonLibrary\acpython\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2AD077-66D0-4A7F-B922-BFEEFAA5EEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91345CE4-7036-4FE3-BA58-8AF9B7150CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{E4F5F74F-CE3A-4B04-BDB8-F19696AB784F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{E4F5F74F-CE3A-4B04-BDB8-F19696AB784F}"/>
   </bookViews>
   <sheets>
     <sheet name="セグ木" sheetId="1" r:id="rId1"/>
     <sheet name="木構造" sheetId="2" r:id="rId2"/>
     <sheet name="たたみ込み" sheetId="3" r:id="rId3"/>
     <sheet name="場合の数" sheetId="4" r:id="rId4"/>
+    <sheet name="BFS" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="203">
   <si>
     <t>Point</t>
     <phoneticPr fontId="1"/>
@@ -1390,6 +1391,65 @@
   </si>
   <si>
     <t>O(nk)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bfs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>startから各地点の距離 通れない箇所は-1</t>
+    <rPh sb="7" eb="10">
+      <t>カクチテン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bfs2Goal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>startからgoalまでの距離 通れない場合は-1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>get_shortest_path_graph</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>startからgoalまでの最短距離に使用するパスのみのグラフ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各辺について、その 辺を除いたときの最短路長</t>
+    <rPh sb="0" eb="2">
+      <t>カクヘン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>startを始点とする最短路木</t>
+    <rPh sb="6" eb="8">
+      <t>シテン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サイタン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ミチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2998,4 +3058,53 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08757771-EDBA-4DE4-832F-7560BF826338}">
+  <dimension ref="B2:C6"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="31.19921875" customWidth="1"/>
+    <col min="3" max="3" width="53.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="C5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="C6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/acpython/検討資料.xlsx
+++ b/acpython/検討資料.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\github\nasu\PythonLibrary\acpython\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91345CE4-7036-4FE3-BA58-8AF9B7150CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACEA2226-B7FA-40C0-AE7C-EE5F6B3A465D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{E4F5F74F-CE3A-4B04-BDB8-F19696AB784F}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="5" xr2:uid="{E4F5F74F-CE3A-4B04-BDB8-F19696AB784F}"/>
   </bookViews>
   <sheets>
     <sheet name="セグ木" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="たたみ込み" sheetId="3" r:id="rId3"/>
     <sheet name="場合の数" sheetId="4" r:id="rId4"/>
     <sheet name="BFS" sheetId="5" r:id="rId5"/>
+    <sheet name="acl" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="208">
   <si>
     <t>Point</t>
     <phoneticPr fontId="1"/>
@@ -1449,6 +1450,30 @@
     </rPh>
     <rPh sb="14" eb="15">
       <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■インストール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pip install git+https://github.com/not522/ac-library-python</t>
+  </si>
+  <si>
+    <t>ACL Practice Contestをac-library-pythonで解いてみたよ。(A～F問題) #Python - Qiita</t>
+  </si>
+  <si>
+    <t>■参考</t>
+    <rPh sb="1" eb="3">
+      <t>サンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大マッチング</t>
+    <rPh sb="0" eb="2">
+      <t>サイダイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3107,4 +3132,43 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E28B3B-5D1C-490E-9ACB-96AA8B5AFE70}">
+  <dimension ref="B2:B14"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B6" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>207</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" display="https://qiita.com/hyouchun/items/4958618268407a5442cc" xr:uid="{3868379A-FFB2-4E99-8064-6FB0D7B89284}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/acpython/検討資料.xlsx
+++ b/acpython/検討資料.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\github\nasu\PythonLibrary\acpython\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACEA2226-B7FA-40C0-AE7C-EE5F6B3A465D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0032DA12-A4AA-45F0-A5B3-ABF8D344CE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="5" xr2:uid="{E4F5F74F-CE3A-4B04-BDB8-F19696AB784F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{E4F5F74F-CE3A-4B04-BDB8-F19696AB784F}"/>
   </bookViews>
   <sheets>
     <sheet name="セグ木" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="場合の数" sheetId="4" r:id="rId4"/>
     <sheet name="BFS" sheetId="5" r:id="rId5"/>
     <sheet name="acl" sheetId="6" r:id="rId6"/>
+    <sheet name="IF" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="241">
   <si>
     <t>Point</t>
     <phoneticPr fontId="1"/>
@@ -1475,6 +1476,138 @@
     <rPh sb="0" eb="2">
       <t>サイダイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BFS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dijkstra</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>add_edge</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>add_edge_undirected</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>add_edges</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>add_edges_undirected</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>get_edges</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dist_list</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>shortest_path</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>shortest_tree</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dists_remove_edge</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>shortest_path_graph</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dirmeter</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Graph</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>get_rvs_list</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>getDrectedGraphMinimum</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>getDfsTreeNodes</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dist</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dist_need_path</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>get_bridge</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TreeFactory</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>setByAdjacencyList</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>setByParentList</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>makeTree</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>makeTreeDP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>makeTour</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>makeLca</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>makeAuxiliaryTree</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>makeHld</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tree</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dfs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>getDi</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3171,4 +3304,169 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E496BB3-DD49-44E5-BE42-59D20B25DA23}">
+  <dimension ref="B2:F15"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="22.69921875" customWidth="1"/>
+    <col min="3" max="3" width="22.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>211</v>
+      </c>
+      <c r="F4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>214</v>
+      </c>
+      <c r="D7" t="s">
+        <v>214</v>
+      </c>
+      <c r="F7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E8" t="s">
+        <v>225</v>
+      </c>
+      <c r="F8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" t="s">
+        <v>226</v>
+      </c>
+      <c r="D9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E9" t="s">
+        <v>239</v>
+      </c>
+      <c r="F9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>217</v>
+      </c>
+      <c r="C10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" t="s">
+        <v>240</v>
+      </c>
+      <c r="F10" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C11" t="s">
+        <v>199</v>
+      </c>
+      <c r="F11" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>195</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/acpython/検討資料.xlsx
+++ b/acpython/検討資料.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\github\nasu\PythonLibrary\acpython\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0032DA12-A4AA-45F0-A5B3-ABF8D344CE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFEEB2E-1F82-4D6B-B552-34E5F8B14A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{E4F5F74F-CE3A-4B04-BDB8-F19696AB784F}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="7" xr2:uid="{E4F5F74F-CE3A-4B04-BDB8-F19696AB784F}"/>
   </bookViews>
   <sheets>
     <sheet name="セグ木" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="BFS" sheetId="5" r:id="rId5"/>
     <sheet name="acl" sheetId="6" r:id="rId6"/>
     <sheet name="IF" sheetId="7" r:id="rId7"/>
+    <sheet name="やることメモ" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="247">
   <si>
     <t>Point</t>
     <phoneticPr fontId="1"/>
@@ -1608,6 +1609,35 @@
   </si>
   <si>
     <t>getDi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Suffix Automaton</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Suffix Automaton - よすぽの日記</t>
+  </si>
+  <si>
+    <t>TreeDPの線形化</t>
+    <rPh sb="7" eb="10">
+      <t>センケイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CHTの拡張</t>
+    <rPh sb="4" eb="6">
+      <t>カクチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Relaxed Convlution</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://atcoder.jp/contests/abc315/editorial/6988</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3469,4 +3499,48 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FDABD0F-272E-40DC-95DC-E9753F1A28E1}">
+  <dimension ref="C2:D5"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="3" max="3" width="16.09765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" display="https://yosupo.hatenablog.com/entry/2021/01/31/160215" xr:uid="{D6EF76DB-E5D0-44F9-A1D0-B3DA7FC66701}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{0507B9D3-BA7A-44CD-BC6C-ED7624030D5A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/acpython/検討資料.xlsx
+++ b/acpython/検討資料.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\github\nasu\PythonLibrary\acpython\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFEEB2E-1F82-4D6B-B552-34E5F8B14A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78B733C-05B5-4F79-826A-46A1111EBC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="7" xr2:uid="{E4F5F74F-CE3A-4B04-BDB8-F19696AB784F}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="8" xr2:uid="{E4F5F74F-CE3A-4B04-BDB8-F19696AB784F}"/>
   </bookViews>
   <sheets>
     <sheet name="セグ木" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="acl" sheetId="6" r:id="rId6"/>
     <sheet name="IF" sheetId="7" r:id="rId7"/>
     <sheet name="やることメモ" sheetId="8" r:id="rId8"/>
+    <sheet name="CHTとslopetrick" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="267">
   <si>
     <t>Point</t>
     <phoneticPr fontId="1"/>
@@ -1638,6 +1639,230 @@
   </si>
   <si>
     <t>https://atcoder.jp/contests/abc315/editorial/6988</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>slope trick</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>slopetrick</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>傾き0で分けて整数傾きごとの座標を持つ</t>
+    <rPh sb="0" eb="1">
+      <t>カタム</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイスウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カタム</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ザヒョウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>座標0で分けて整数座標ごとの傾きを持つ</t>
+    <rPh sb="0" eb="2">
+      <t>ザヒョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイスウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ザヒョウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カタム</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左右で分けない、傾きの変化量をpriqueで持つ</t>
+    <rPh sb="0" eb="2">
+      <t>サユウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カタム</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ヘンカリョウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平行二分木（多重集合への区間加算と区間和）</t>
+    <rPh sb="0" eb="2">
+      <t>ヘイコウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ニ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>タジュウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュウゴウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>クカン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カサン</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>クカンワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>線分の畳み込み</t>
+    <rPh sb="0" eb="2">
+      <t>センブン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タタ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>定義域の制限</t>
+    <rPh sb="0" eb="2">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>点取得</t>
+    <rPh sb="0" eb="3">
+      <t>テンシュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最小値取得</t>
+    <rPh sb="0" eb="3">
+      <t>サイショウチ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>f(0)取得</t>
+    <rPh sb="4" eb="6">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>半直線の畳み込み</t>
+    <rPh sb="0" eb="3">
+      <t>ハンチョクセン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>タタミ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>傾き</t>
+    <rPh sb="0" eb="1">
+      <t>カタム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>座標</t>
+    <rPh sb="0" eb="2">
+      <t>ザヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CHT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>直線を追加</t>
+    <rPh sb="0" eb="2">
+      <t>チョクセン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大値を取得</t>
+    <rPh sb="0" eb="2">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最小値を取得</t>
+    <rPh sb="0" eb="3">
+      <t>サイショウチ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シュトク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3503,7 +3728,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FDABD0F-272E-40DC-95DC-E9753F1A28E1}">
-  <dimension ref="C2:D5"/>
+  <dimension ref="C2:D6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="16.09765625" bestFit="1" customWidth="1"/>
@@ -3535,6 +3760,11 @@
         <v>246</v>
       </c>
     </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C6" t="s">
+        <v>247</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -3543,4 +3773,207 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEE05A29-4BCD-499A-8B13-6F67B0AFE7B6}">
+  <dimension ref="B17:H35"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="4" max="4" width="41.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="4.8984375" customWidth="1"/>
+    <col min="11" max="11" width="8.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>248</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="D18" t="s">
+        <v>253</v>
+      </c>
+      <c r="E18" t="s">
+        <v>259</v>
+      </c>
+      <c r="F18" t="s">
+        <v>260</v>
+      </c>
+      <c r="G18" t="s">
+        <v>261</v>
+      </c>
+      <c r="H18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="D19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>259</v>
+      </c>
+      <c r="F19" t="s">
+        <v>260</v>
+      </c>
+      <c r="G19" t="s">
+        <v>261</v>
+      </c>
+      <c r="H19" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="D20" t="s">
+        <v>258</v>
+      </c>
+      <c r="E20" t="s">
+        <v>261</v>
+      </c>
+      <c r="F20" t="s">
+        <v>261</v>
+      </c>
+      <c r="G20" t="s">
+        <v>261</v>
+      </c>
+      <c r="H20" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="D21" t="s">
+        <v>254</v>
+      </c>
+      <c r="E21" t="s">
+        <v>261</v>
+      </c>
+      <c r="F21" t="s">
+        <v>261</v>
+      </c>
+      <c r="G21" t="s">
+        <v>261</v>
+      </c>
+      <c r="H21" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="D22" t="s">
+        <v>255</v>
+      </c>
+      <c r="E22" t="s">
+        <v>262</v>
+      </c>
+      <c r="F22" t="s">
+        <v>262</v>
+      </c>
+      <c r="G22" t="s">
+        <v>262</v>
+      </c>
+      <c r="H22" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="D23" t="s">
+        <v>256</v>
+      </c>
+      <c r="E23" t="s">
+        <v>261</v>
+      </c>
+      <c r="F23" t="s">
+        <v>262</v>
+      </c>
+      <c r="G23" t="s">
+        <v>262</v>
+      </c>
+      <c r="H23" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="D24" t="s">
+        <v>257</v>
+      </c>
+      <c r="E24" t="s">
+        <v>262</v>
+      </c>
+      <c r="F24" t="s">
+        <v>261</v>
+      </c>
+      <c r="G24" t="s">
+        <v>262</v>
+      </c>
+      <c r="H24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>263</v>
+      </c>
+      <c r="D33" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="D34" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="D35" t="s">
+        <v>266</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>